--- a/Código/Controles/14. Ordenamiento de columnas (Ballotage).xlsx
+++ b/Código/Controles/14. Ordenamiento de columnas (Ballotage).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:MU51"/>
+  <dimension ref="A1:MI51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,130 +2096,70 @@
       </c>
       <c r="LV1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Opinion_Pro</t>
+          <t>Sentimiento_Fase_Final</t>
         </is>
       </c>
       <c r="LW1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Tiempo_Pro</t>
+          <t>Evento_Estresante</t>
         </is>
       </c>
       <c r="LX1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Opinion_Con</t>
+          <t>Sabia_Del_Experimento</t>
         </is>
       </c>
       <c r="LY1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Tiempo_Con</t>
+          <t>Usa_Sustancias</t>
         </is>
       </c>
       <c r="LZ1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Opinion_Pro_Izq</t>
+          <t>Tabaco</t>
         </is>
       </c>
       <c r="MA1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Tiempo_Pro_Izq</t>
+          <t>Alcohol</t>
         </is>
       </c>
       <c r="MB1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Opinion_Pro_Der</t>
+          <t>Marihuana</t>
         </is>
       </c>
       <c r="MC1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Tiempo_Pro_Der</t>
+          <t>Drogas_Recreativas</t>
         </is>
       </c>
       <c r="MD1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Opinion_Con_Izq</t>
+          <t>Cual_Droga_Recreativa</t>
         </is>
       </c>
       <c r="ME1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Tiempo_Con_Izq</t>
+          <t>Medicamentos</t>
         </is>
       </c>
       <c r="MF1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Opinion_Con_Der</t>
+          <t>Cual_Medicamento</t>
         </is>
       </c>
       <c r="MG1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Tiempo_Con_Der</t>
+          <t>Otras_Sustancias</t>
         </is>
       </c>
       <c r="MH1" s="1" t="inlineStr">
         <is>
-          <t>Sentimiento_Fase_Final</t>
+          <t>Horas_Sueno_Promedio</t>
         </is>
       </c>
       <c r="MI1" s="1" t="inlineStr">
-        <is>
-          <t>Evento_Estresante</t>
-        </is>
-      </c>
-      <c r="MJ1" s="1" t="inlineStr">
-        <is>
-          <t>Sabia_Del_Experimento</t>
-        </is>
-      </c>
-      <c r="MK1" s="1" t="inlineStr">
-        <is>
-          <t>Usa_Sustancias</t>
-        </is>
-      </c>
-      <c r="ML1" s="1" t="inlineStr">
-        <is>
-          <t>Tabaco</t>
-        </is>
-      </c>
-      <c r="MM1" s="1" t="inlineStr">
-        <is>
-          <t>Alcohol</t>
-        </is>
-      </c>
-      <c r="MN1" s="1" t="inlineStr">
-        <is>
-          <t>Marihuana</t>
-        </is>
-      </c>
-      <c r="MO1" s="1" t="inlineStr">
-        <is>
-          <t>Drogas_Recreativas</t>
-        </is>
-      </c>
-      <c r="MP1" s="1" t="inlineStr">
-        <is>
-          <t>Cual_Droga_Recreativa</t>
-        </is>
-      </c>
-      <c r="MQ1" s="1" t="inlineStr">
-        <is>
-          <t>Medicamentos</t>
-        </is>
-      </c>
-      <c r="MR1" s="1" t="inlineStr">
-        <is>
-          <t>Cual_Medicamento</t>
-        </is>
-      </c>
-      <c r="MS1" s="1" t="inlineStr">
-        <is>
-          <t>Otras_Sustancias</t>
-        </is>
-      </c>
-      <c r="MT1" s="1" t="inlineStr">
-        <is>
-          <t>Horas_Sueno_Promedio</t>
-        </is>
-      </c>
-      <c r="MU1" s="1" t="inlineStr">
         <is>
           <t>Sueno_Noche_Anterior</t>
         </is>
@@ -3211,108 +3151,72 @@
       <c r="LU2" t="n">
         <v>11.4523125</v>
       </c>
-      <c r="LV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG2" t="n">
-        <v>0</v>
+      <c r="LV2" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY2" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ2" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA2" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB2" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD2" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME2" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MF2" t="inlineStr">
+        <is>
+          <t>levotiroxina y anticonceptivas</t>
+        </is>
+      </c>
+      <c r="MG2" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH2" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK2" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML2" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM2" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN2" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP2" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ2" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MR2" t="inlineStr">
-        <is>
-          <t>levotiroxina y anticonceptivas</t>
-        </is>
-      </c>
-      <c r="MS2" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT2" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU2" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -4304,108 +4208,72 @@
       <c r="LU3" t="n">
         <v>8.569187500000002</v>
       </c>
-      <c r="LV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG3" t="n">
-        <v>0</v>
+      <c r="LV3" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY3" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="LZ3" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MA3" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB3" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MC3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD3" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME3" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF3" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG3" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH3" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>3-5 horas</t>
         </is>
       </c>
       <c r="MI3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK3" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="ML3" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MM3" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN3" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MO3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP3" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ3" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR3" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS3" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT3" t="inlineStr">
-        <is>
-          <t>3-5 horas</t>
-        </is>
-      </c>
-      <c r="MU3" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -5397,108 +5265,72 @@
       <c r="LU4" t="n">
         <v>5.210000000000001</v>
       </c>
-      <c r="LV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG4" t="n">
-        <v>0</v>
+      <c r="LV4" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY4" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="LZ4" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MA4" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MB4" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MC4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MD4" t="inlineStr">
+        <is>
+          <t>marihuana</t>
+        </is>
+      </c>
+      <c r="ME4" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF4" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG4" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH4" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK4" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ML4" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MM4" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="MN4" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MO4" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MP4" t="inlineStr">
-        <is>
-          <t>marihuana</t>
-        </is>
-      </c>
-      <c r="MQ4" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR4" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS4" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT4" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU4" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -6490,108 +6322,72 @@
       <c r="LU5" t="n">
         <v>6.301166666666667</v>
       </c>
-      <c r="LV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG5" t="n">
-        <v>0</v>
+      <c r="LV5" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX5" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LY5" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ5" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA5" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB5" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD5" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME5" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF5" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG5" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH5" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ5" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MK5" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML5" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM5" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN5" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP5" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ5" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR5" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS5" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT5" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU5" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -7583,108 +7379,72 @@
       <c r="LU6" t="n">
         <v>5.285</v>
       </c>
-      <c r="LV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG6" t="n">
-        <v>0</v>
+      <c r="LV6" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LY6" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ6" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA6" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB6" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD6" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME6" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF6" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG6" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH6" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ6" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MK6" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML6" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM6" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN6" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP6" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ6" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR6" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS6" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT6" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU6" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -8676,108 +8436,72 @@
       <c r="LU7" t="n">
         <v>7.8445</v>
       </c>
-      <c r="LV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG7" t="n">
-        <v>0</v>
+      <c r="LV7" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX7" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LY7" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ7" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA7" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MB7" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD7" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME7" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF7" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG7" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH7" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>mas de 8 horas</t>
         </is>
       </c>
       <c r="MI7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ7" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MK7" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML7" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM7" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="MN7" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP7" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ7" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR7" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS7" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT7" t="inlineStr">
-        <is>
-          <t>mas de 8 horas</t>
-        </is>
-      </c>
-      <c r="MU7" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -9769,108 +9493,72 @@
       <c r="LU8" t="n">
         <v>5.8797</v>
       </c>
-      <c r="LV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG8" t="n">
-        <v>0</v>
+      <c r="LV8" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX8" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LY8" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ8" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA8" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB8" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD8" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME8" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF8" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG8" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH8" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ8" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MK8" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML8" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM8" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN8" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP8" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ8" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR8" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS8" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT8" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU8" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -10862,108 +10550,72 @@
       <c r="LU9" t="n">
         <v>6.997125</v>
       </c>
-      <c r="LV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG9" t="n">
-        <v>0</v>
+      <c r="LV9" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY9" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="LZ9" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MA9" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB9" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MC9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD9" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME9" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF9" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG9" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH9" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK9" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="ML9" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MM9" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN9" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MO9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP9" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ9" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR9" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS9" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT9" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU9" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -11955,108 +11607,72 @@
       <c r="LU10" t="n">
         <v>6.7235</v>
       </c>
-      <c r="LV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG10" t="n">
-        <v>0</v>
+      <c r="LV10" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY10" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="LZ10" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MA10" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MB10" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MC10" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MD10" t="inlineStr">
+        <is>
+          <t>marihuana</t>
+        </is>
+      </c>
+      <c r="ME10" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MF10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">antidepresivos </t>
+        </is>
+      </c>
+      <c r="MG10" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH10" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK10" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ML10" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MM10" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="MN10" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MO10" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MP10" t="inlineStr">
-        <is>
-          <t>marihuana</t>
-        </is>
-      </c>
-      <c r="MQ10" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MR10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">antidepresivos </t>
-        </is>
-      </c>
-      <c r="MS10" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT10" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU10" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -13048,104 +12664,68 @@
       <c r="LU11" t="n">
         <v>56.283875</v>
       </c>
-      <c r="LV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG11" t="n">
-        <v>0</v>
+      <c r="LV11" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="LW11" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY11" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ11" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA11" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB11" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD11" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME11" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MF11" t="inlineStr"/>
+      <c r="MG11" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH11" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI11" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK11" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML11" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM11" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN11" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP11" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ11" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MR11" t="inlineStr"/>
-      <c r="MS11" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT11" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU11" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -14137,108 +13717,72 @@
       <c r="LU12" t="n">
         <v>11.2459</v>
       </c>
-      <c r="LV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG12" t="n">
-        <v>0</v>
+      <c r="LV12" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW12" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY12" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ12" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA12" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB12" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD12" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME12" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF12" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG12" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH12" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI12" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK12" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML12" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM12" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN12" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP12" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ12" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR12" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS12" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT12" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU12" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -15230,108 +14774,72 @@
       <c r="LU13" t="n">
         <v>22.82916666666666</v>
       </c>
-      <c r="LV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG13" t="n">
-        <v>0</v>
+      <c r="LV13" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY13" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="LZ13" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MA13" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MB13" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MC13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD13" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME13" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF13" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG13" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH13" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK13" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ML13" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MM13" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="MN13" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MO13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP13" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ13" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR13" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS13" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT13" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU13" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -16323,108 +15831,72 @@
       <c r="LU14" t="n">
         <v>8.4011</v>
       </c>
-      <c r="LV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG14" t="n">
-        <v>0</v>
+      <c r="LV14" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY14" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ14" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA14" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB14" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD14" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME14" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MF14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">levotiroxina y para la presión </t>
+        </is>
+      </c>
+      <c r="MG14" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH14" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK14" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML14" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM14" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN14" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP14" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ14" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MR14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">levotiroxina y para la presión </t>
-        </is>
-      </c>
-      <c r="MS14" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT14" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU14" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -17416,104 +16888,68 @@
       <c r="LU15" t="n">
         <v>9.274714285714285</v>
       </c>
-      <c r="LV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG15" t="n">
-        <v>0</v>
+      <c r="LV15" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY15" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="LZ15" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MA15" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB15" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MC15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD15" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME15" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MF15" t="inlineStr"/>
+      <c r="MG15" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH15" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK15" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="ML15" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MM15" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN15" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MO15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP15" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ15" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MR15" t="inlineStr"/>
-      <c r="MS15" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT15" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU15" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -18505,108 +17941,72 @@
       <c r="LU16" t="n">
         <v>7.480357142857143</v>
       </c>
-      <c r="LV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG16" t="n">
-        <v>0</v>
+      <c r="LV16" t="inlineStr">
+        <is>
+          <t>nervioso</t>
+        </is>
+      </c>
+      <c r="LW16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX16" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LY16" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ16" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA16" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB16" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD16" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME16" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF16" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG16" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH16" t="inlineStr">
         <is>
-          <t>nervioso</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ16" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MK16" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML16" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM16" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN16" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP16" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ16" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR16" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS16" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT16" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU16" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -19598,108 +18998,72 @@
       <c r="LU17" t="n">
         <v>12.79275</v>
       </c>
-      <c r="LV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG17" t="n">
-        <v>0</v>
+      <c r="LV17" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW17" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY17" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ17" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA17" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB17" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MC17" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MD17" t="inlineStr">
+        <is>
+          <t>cbd</t>
+        </is>
+      </c>
+      <c r="ME17" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MF17" t="inlineStr">
+        <is>
+          <t>fexofenadina</t>
+        </is>
+      </c>
+      <c r="MG17" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH17" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI17" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK17" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML17" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM17" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN17" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MO17" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MP17" t="inlineStr">
-        <is>
-          <t>cbd</t>
-        </is>
-      </c>
-      <c r="MQ17" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="MR17" t="inlineStr">
-        <is>
-          <t>fexofenadina</t>
-        </is>
-      </c>
-      <c r="MS17" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT17" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU17" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -20691,108 +20055,72 @@
       <c r="LU18" t="n">
         <v>20.5192</v>
       </c>
-      <c r="LV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG18" t="n">
-        <v>0</v>
+      <c r="LV18" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY18" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ18" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA18" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MB18" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD18" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME18" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF18" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG18" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH18" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK18" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML18" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM18" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="MN18" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP18" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ18" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR18" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS18" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT18" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU18" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -21784,108 +21112,72 @@
       <c r="LU19" t="n">
         <v>5.732125</v>
       </c>
-      <c r="LV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG19" t="n">
-        <v>0</v>
+      <c r="LV19" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX19" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LY19" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ19" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA19" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MB19" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD19" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME19" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MF19" t="inlineStr">
+        <is>
+          <t>fluoxetina</t>
+        </is>
+      </c>
+      <c r="MG19" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH19" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ19" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MK19" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML19" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM19" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="MN19" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP19" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ19" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MR19" t="inlineStr">
-        <is>
-          <t>fluoxetina</t>
-        </is>
-      </c>
-      <c r="MS19" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT19" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU19" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -22877,108 +22169,72 @@
       <c r="LU20" t="n">
         <v>7.211</v>
       </c>
-      <c r="LV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG20" t="n">
-        <v>0</v>
+      <c r="LV20" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW20" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY20" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="LZ20" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MA20" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB20" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD20" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME20" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF20" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG20" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH20" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI20" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK20" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ML20" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MM20" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN20" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP20" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ20" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR20" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS20" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT20" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU20" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -23970,108 +23226,72 @@
       <c r="LU21" t="n">
         <v>7.6854</v>
       </c>
-      <c r="LV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG21" t="n">
-        <v>0</v>
+      <c r="LV21" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY21" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="LZ21" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MA21" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB21" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MC21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD21" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME21" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF21" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG21" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH21" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK21" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ML21" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MM21" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN21" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MO21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP21" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ21" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR21" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS21" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT21" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU21" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -25063,108 +24283,72 @@
       <c r="LU22" t="n">
         <v>12.339</v>
       </c>
-      <c r="LV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG22" t="n">
-        <v>0</v>
+      <c r="LV22" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW22" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY22" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ22" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA22" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB22" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD22" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME22" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF22" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG22" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH22" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI22" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK22" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML22" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM22" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN22" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP22" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ22" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR22" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS22" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT22" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU22" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -26156,108 +25340,72 @@
       <c r="LU23" t="n">
         <v>10.2644</v>
       </c>
-      <c r="LV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG23" t="n">
-        <v>0</v>
+      <c r="LV23" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY23" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ23" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA23" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB23" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD23" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME23" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF23" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG23" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH23" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK23" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML23" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM23" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN23" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP23" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ23" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR23" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS23" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT23" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU23" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -27249,108 +26397,72 @@
       <c r="LU24" t="n">
         <v>5.061125000000001</v>
       </c>
-      <c r="LV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG24" t="n">
-        <v>0</v>
+      <c r="LV24" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW24" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY24" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="LZ24" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MA24" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB24" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD24" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME24" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MF24" t="inlineStr">
+        <is>
+          <t>analgesicos</t>
+        </is>
+      </c>
+      <c r="MG24" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH24" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI24" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK24" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ML24" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MM24" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN24" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP24" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ24" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MR24" t="inlineStr">
-        <is>
-          <t>analgesicos</t>
-        </is>
-      </c>
-      <c r="MS24" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT24" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU24" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -28342,108 +27454,72 @@
       <c r="LU25" t="n">
         <v>11.213</v>
       </c>
-      <c r="LV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG25" t="n">
-        <v>0</v>
+      <c r="LV25" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW25" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY25" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ25" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA25" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB25" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD25" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME25" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF25" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG25" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH25" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI25" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK25" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML25" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM25" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN25" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP25" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ25" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR25" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS25" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT25" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU25" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -29435,108 +28511,72 @@
       <c r="LU26" t="n">
         <v>9.297583333333334</v>
       </c>
-      <c r="LV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG26" t="n">
-        <v>0</v>
+      <c r="LV26" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW26" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY26" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="LZ26" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MA26" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB26" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MC26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD26" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME26" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF26" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG26" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH26" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI26" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK26" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="ML26" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MM26" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN26" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MO26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP26" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ26" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR26" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS26" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT26" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU26" t="inlineStr">
         <is>
           <t>mas de 8 horas</t>
         </is>
@@ -30528,108 +29568,72 @@
       <c r="LU27" t="n">
         <v>6.710714285714285</v>
       </c>
-      <c r="LV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG27" t="n">
-        <v>0</v>
+      <c r="LV27" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY27" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ27" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA27" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB27" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD27" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME27" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF27" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG27" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH27" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK27" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML27" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM27" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN27" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP27" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ27" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR27" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS27" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT27" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU27" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -31621,108 +30625,72 @@
       <c r="LU28" t="n">
         <v>9.739583333333334</v>
       </c>
-      <c r="LV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG28" t="n">
-        <v>0</v>
+      <c r="LV28" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY28" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="LZ28" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MA28" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB28" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD28" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME28" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF28" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG28" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH28" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>3-5 horas</t>
         </is>
       </c>
       <c r="MI28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK28" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ML28" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MM28" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN28" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP28" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ28" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR28" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS28" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT28" t="inlineStr">
-        <is>
-          <t>3-5 horas</t>
-        </is>
-      </c>
-      <c r="MU28" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -32714,108 +31682,72 @@
       <c r="LU29" t="n">
         <v>25.1878</v>
       </c>
-      <c r="LV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG29" t="n">
-        <v>0</v>
+      <c r="LV29" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="LW29" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY29" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ29" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA29" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB29" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD29" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME29" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MF29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analgésico </t>
+        </is>
+      </c>
+      <c r="MG29" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH29" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI29" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK29" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML29" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM29" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN29" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP29" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ29" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MR29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">analgésico </t>
-        </is>
-      </c>
-      <c r="MS29" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT29" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU29" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -33807,108 +32739,72 @@
       <c r="LU30" t="n">
         <v>11.5829</v>
       </c>
-      <c r="LV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG30" t="n">
-        <v>0</v>
+      <c r="LV30" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY30" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="LZ30" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MA30" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB30" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD30" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME30" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF30" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG30" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH30" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK30" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ML30" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MM30" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN30" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP30" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ30" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR30" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS30" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT30" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU30" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -34900,108 +33796,72 @@
       <c r="LU31" t="n">
         <v>5.991416666666666</v>
       </c>
-      <c r="LV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG31" t="n">
-        <v>0</v>
+      <c r="LV31" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY31" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="LZ31" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MA31" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB31" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD31" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME31" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MF31" t="inlineStr">
+        <is>
+          <t>antidepresivo</t>
+        </is>
+      </c>
+      <c r="MG31" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH31" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>mas de 8 horas</t>
         </is>
       </c>
       <c r="MI31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK31" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="ML31" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="MM31" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN31" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP31" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ31" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MR31" t="inlineStr">
-        <is>
-          <t>antidepresivo</t>
-        </is>
-      </c>
-      <c r="MS31" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT31" t="inlineStr">
-        <is>
-          <t>mas de 8 horas</t>
-        </is>
-      </c>
-      <c r="MU31" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -35993,108 +34853,72 @@
       <c r="LU32" t="n">
         <v>33.0031</v>
       </c>
-      <c r="LV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG32" t="n">
-        <v>0</v>
+      <c r="LV32" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW32" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY32" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ32" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA32" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MB32" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD32" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME32" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MF32" t="inlineStr">
+        <is>
+          <t>antidepresivo</t>
+        </is>
+      </c>
+      <c r="MG32" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH32" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI32" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK32" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML32" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM32" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="MN32" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP32" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ32" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MR32" t="inlineStr">
-        <is>
-          <t>antidepresivo</t>
-        </is>
-      </c>
-      <c r="MS32" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT32" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU32" t="inlineStr">
         <is>
           <t>mas de 8 horas</t>
         </is>
@@ -37086,108 +35910,72 @@
       <c r="LU33" t="n">
         <v>6.025</v>
       </c>
-      <c r="LV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG33" t="n">
-        <v>0</v>
+      <c r="LV33" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW33" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY33" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="LZ33" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MA33" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB33" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD33" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME33" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF33" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG33" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH33" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI33" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK33" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ML33" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MM33" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN33" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP33" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ33" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR33" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS33" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT33" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU33" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -38179,108 +36967,72 @@
       <c r="LU34" t="n">
         <v>8.366999999999999</v>
       </c>
-      <c r="LV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG34" t="n">
-        <v>0</v>
+      <c r="LV34" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY34" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ34" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA34" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB34" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MC34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD34" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME34" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF34" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG34" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH34" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK34" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML34" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM34" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN34" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MO34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP34" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ34" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR34" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS34" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT34" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU34" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -39272,108 +38024,72 @@
       <c r="LU35" t="n">
         <v>6.046875</v>
       </c>
-      <c r="LV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW35" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX35" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY35" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG35" t="n">
-        <v>0</v>
+      <c r="LV35" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW35" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY35" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="LZ35" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MA35" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB35" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD35" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME35" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MF35" t="inlineStr">
+        <is>
+          <t>velanfaxina</t>
+        </is>
+      </c>
+      <c r="MG35" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH35" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI35" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK35" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="ML35" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MM35" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN35" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP35" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ35" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MR35" t="inlineStr">
-        <is>
-          <t>velanfaxina</t>
-        </is>
-      </c>
-      <c r="MS35" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT35" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU35" t="inlineStr">
         <is>
           <t>mas de 8 horas</t>
         </is>
@@ -40365,108 +39081,72 @@
       <c r="LU36" t="n">
         <v>9.08445</v>
       </c>
-      <c r="LV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG36" t="n">
-        <v>0</v>
+      <c r="LV36" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX36" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LY36" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ36" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA36" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB36" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD36" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME36" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF36" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG36" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH36" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ36" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MK36" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML36" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM36" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN36" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP36" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ36" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR36" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS36" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT36" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU36" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -41458,108 +40138,72 @@
       <c r="LU37" t="n">
         <v>4.374700000000001</v>
       </c>
-      <c r="LV37" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW37" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX37" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY37" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG37" t="n">
-        <v>0</v>
+      <c r="LV37" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="LW37" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY37" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ37" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA37" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB37" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MC37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD37" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME37" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MF37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">antihistaminicos y antiacidos </t>
+        </is>
+      </c>
+      <c r="MG37" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH37" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI37" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK37" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML37" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM37" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN37" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MO37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP37" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ37" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MR37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">antihistaminicos y antiacidos </t>
-        </is>
-      </c>
-      <c r="MS37" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT37" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU37" t="inlineStr">
         <is>
           <t>mas de 8 horas</t>
         </is>
@@ -42551,108 +41195,72 @@
       <c r="LU38" t="n">
         <v>12.86008333333333</v>
       </c>
-      <c r="LV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW38" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX38" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY38" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG38" t="n">
-        <v>0</v>
+      <c r="LV38" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX38" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LY38" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ38" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA38" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB38" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MC38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD38" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME38" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF38" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG38" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH38" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ38" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MK38" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML38" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM38" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN38" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MO38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP38" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ38" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR38" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS38" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT38" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU38" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -43644,108 +42252,72 @@
       <c r="LU39" t="n">
         <v>14.9699</v>
       </c>
-      <c r="LV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG39" t="n">
-        <v>0</v>
+      <c r="LV39" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX39" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LY39" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ39" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA39" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB39" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD39" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME39" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MF39" t="inlineStr">
+        <is>
+          <t>metformina. rosuvastatina</t>
+        </is>
+      </c>
+      <c r="MG39" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH39" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ39" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MK39" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML39" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM39" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN39" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP39" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ39" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MR39" t="inlineStr">
-        <is>
-          <t>metformina. rosuvastatina</t>
-        </is>
-      </c>
-      <c r="MS39" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT39" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU39" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -44737,108 +43309,72 @@
       <c r="LU40" t="n">
         <v>9.391500000000001</v>
       </c>
-      <c r="LV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY40" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG40" t="n">
-        <v>0</v>
+      <c r="LV40" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX40" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LY40" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ40" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA40" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MB40" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD40" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME40" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF40" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG40" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH40" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ40" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MK40" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML40" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM40" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="MN40" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP40" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ40" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR40" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS40" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT40" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU40" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -45830,108 +44366,72 @@
       <c r="LU41" t="n">
         <v>9.853166666666667</v>
       </c>
-      <c r="LV41" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW41" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX41" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY41" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG41" t="n">
-        <v>0</v>
+      <c r="LV41" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY41" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ41" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA41" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB41" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD41" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME41" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MF41" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG41" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH41" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK41" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML41" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM41" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN41" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP41" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ41" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MR41" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS41" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT41" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU41" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -46923,108 +45423,72 @@
       <c r="LU42" t="n">
         <v>24.22025</v>
       </c>
-      <c r="LV42" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW42" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX42" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY42" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG42" t="n">
-        <v>0</v>
+      <c r="LV42" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY42" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="LZ42" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MA42" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB42" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD42" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME42" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MF42" t="inlineStr">
+        <is>
+          <t>omeprazol y cetirizina diclorhidrato</t>
+        </is>
+      </c>
+      <c r="MG42" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH42" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK42" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ML42" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MM42" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN42" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP42" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ42" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MR42" t="inlineStr">
-        <is>
-          <t>omeprazol y cetirizina diclorhidrato</t>
-        </is>
-      </c>
-      <c r="MS42" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT42" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU42" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -48016,108 +46480,72 @@
       <c r="LU43" t="n">
         <v>4.96225</v>
       </c>
-      <c r="LV43" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW43" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX43" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY43" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG43" t="n">
-        <v>0</v>
+      <c r="LV43" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY43" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ43" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA43" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB43" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD43" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME43" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF43" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG43" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH43" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK43" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML43" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM43" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN43" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP43" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ43" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR43" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS43" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT43" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU43" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -49109,108 +47537,72 @@
       <c r="LU44" t="n">
         <v>6.325625</v>
       </c>
-      <c r="LV44" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW44" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX44" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY44" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG44" t="n">
-        <v>0</v>
+      <c r="LV44" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW44" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY44" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ44" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA44" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB44" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD44" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME44" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MF44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeopatía </t>
+        </is>
+      </c>
+      <c r="MG44" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
       </c>
       <c r="MH44" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI44" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK44" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML44" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM44" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN44" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP44" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ44" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MR44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">homeopatía </t>
-        </is>
-      </c>
-      <c r="MS44" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MT44" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU44" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -50202,108 +48594,72 @@
       <c r="LU45" t="n">
         <v>6.0011</v>
       </c>
-      <c r="LV45" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW45" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX45" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY45" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG45" t="n">
-        <v>0</v>
+      <c r="LV45" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW45" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX45" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LY45" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ45" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA45" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB45" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD45" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME45" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MF45" t="inlineStr">
+        <is>
+          <t>acenocumarol/ t4/ metformina</t>
+        </is>
+      </c>
+      <c r="MG45" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH45" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI45" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ45" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MK45" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML45" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM45" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN45" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP45" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ45" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MR45" t="inlineStr">
-        <is>
-          <t>acenocumarol/ t4/ metformina</t>
-        </is>
-      </c>
-      <c r="MS45" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT45" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU45" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -51295,108 +49651,72 @@
       <c r="LU46" t="n">
         <v>11.75305</v>
       </c>
-      <c r="LV46" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW46" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX46" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY46" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG46" t="n">
-        <v>0</v>
+      <c r="LV46" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY46" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ46" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA46" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB46" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MC46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD46" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME46" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF46" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG46" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH46" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK46" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML46" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM46" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN46" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MO46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP46" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ46" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR46" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS46" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT46" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU46" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -52388,108 +50708,72 @@
       <c r="LU47" t="n">
         <v>9.956833333333334</v>
       </c>
-      <c r="LV47" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW47" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX47" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY47" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG47" t="n">
-        <v>0</v>
+      <c r="LV47" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY47" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ47" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA47" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MB47" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MC47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD47" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME47" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF47" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG47" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH47" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK47" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML47" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM47" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MN47" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MO47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP47" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ47" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR47" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS47" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT47" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU47" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -53481,108 +51765,72 @@
       <c r="LU48" t="n">
         <v>11.8397</v>
       </c>
-      <c r="LV48" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW48" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX48" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY48" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG48" t="n">
-        <v>0</v>
+      <c r="LV48" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY48" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ48" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA48" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB48" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD48" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME48" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MF48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">insulina </t>
+        </is>
+      </c>
+      <c r="MG48" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH48" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK48" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML48" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM48" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN48" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP48" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ48" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MR48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">insulina </t>
-        </is>
-      </c>
-      <c r="MS48" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT48" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU48" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -54574,108 +52822,72 @@
       <c r="LU49" t="n">
         <v>4.816071428571429</v>
       </c>
-      <c r="LV49" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW49" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX49" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY49" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG49" t="n">
-        <v>0</v>
+      <c r="LV49" t="inlineStr">
+        <is>
+          <t>nervioso</t>
+        </is>
+      </c>
+      <c r="LW49" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="LX49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY49" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ49" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA49" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MB49" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MC49" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MD49" t="inlineStr">
+        <is>
+          <t>cerveza</t>
+        </is>
+      </c>
+      <c r="ME49" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MF49" t="inlineStr">
+        <is>
+          <t>me automedico con tafirol</t>
+        </is>
+      </c>
+      <c r="MG49" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH49" t="inlineStr">
         <is>
-          <t>nervioso</t>
+          <t>mas de 8 horas</t>
         </is>
       </c>
       <c r="MI49" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MJ49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK49" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML49" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM49" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MN49" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MO49" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="MP49" t="inlineStr">
-        <is>
-          <t>cerveza</t>
-        </is>
-      </c>
-      <c r="MQ49" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="MR49" t="inlineStr">
-        <is>
-          <t>me automedico con tafirol</t>
-        </is>
-      </c>
-      <c r="MS49" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT49" t="inlineStr">
-        <is>
-          <t>mas de 8 horas</t>
-        </is>
-      </c>
-      <c r="MU49" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -55667,108 +53879,72 @@
       <c r="LU50" t="n">
         <v>5.497</v>
       </c>
-      <c r="LV50" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW50" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX50" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY50" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG50" t="n">
-        <v>0</v>
+      <c r="LV50" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY50" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ50" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA50" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MB50" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD50" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME50" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MF50" t="inlineStr">
+        <is>
+          <t>levotixina, sertralina</t>
+        </is>
+      </c>
+      <c r="MG50" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH50" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK50" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML50" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM50" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="MN50" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP50" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ50" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="MR50" t="inlineStr">
-        <is>
-          <t>levotixina, sertralina</t>
-        </is>
-      </c>
-      <c r="MS50" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT50" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU50" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -56760,108 +54936,72 @@
       <c r="LU51" t="n">
         <v>5.907083333333333</v>
       </c>
-      <c r="LV51" t="n">
-        <v>0</v>
-      </c>
-      <c r="LW51" t="n">
-        <v>0</v>
-      </c>
-      <c r="LX51" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY51" t="n">
-        <v>0</v>
-      </c>
-      <c r="LZ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="ME51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MG51" t="n">
-        <v>0</v>
+      <c r="LV51" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="LW51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LX51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="LY51" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="LZ51" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MA51" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MB51" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MC51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MD51" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="ME51" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MF51" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MG51" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MH51" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MI51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MJ51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MK51" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ML51" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MM51" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MN51" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MO51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="MP51" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MQ51" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MR51" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="MS51" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="MT51" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="MU51" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
